--- a/Excel Forecast/Test_Excel.xlsx
+++ b/Excel Forecast/Test_Excel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wangb\Angular\CSCInventoryForecast\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBC95680-CDF0-4A7C-B061-BCBED16F9C3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C318B7A0-99E0-4BF5-8DF3-F916E290AFBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3984" yWindow="2520" windowWidth="18432" windowHeight="12120" activeTab="1" xr2:uid="{86BFF98B-835F-49C6-A17D-9A3C97C37DB2}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="24792" windowHeight="14856" activeTab="1" xr2:uid="{86BFF98B-835F-49C6-A17D-9A3C97C37DB2}"/>
   </bookViews>
   <sheets>
     <sheet name="2024" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="571" uniqueCount="264">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="269">
   <si>
     <t>SKU</t>
   </si>
@@ -829,13 +829,28 @@
   </si>
   <si>
     <t>Annual Sales in Excel</t>
+  </si>
+  <si>
+    <t>OAKVILLE</t>
+  </si>
+  <si>
+    <t>VANCOUVER</t>
+  </si>
+  <si>
+    <t>KK-11506</t>
+  </si>
+  <si>
+    <t>KK-11508</t>
+  </si>
+  <si>
+    <t>KK-11510</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -848,6 +863,10 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
     </font>
   </fonts>
   <fills count="2">
@@ -905,10 +924,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -918,9 +938,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{BF4C1658-BD8E-4B26-B7C7-94F68468541B}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1253,7 +1277,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DA4A3C4-D69A-4D3D-B4C9-10832B0889C1}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1261,15 +1285,19 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29B3801E-FE66-4357-B2C8-564E136A780E}">
-  <dimension ref="A1:O274"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:O298"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="17.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.5546875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15">
       <c r="A1" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15">
       <c r="A2" t="s">
         <v>262</v>
       </c>
@@ -1310,7 +1338,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -1357,7 +1385,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15">
       <c r="A4" s="4" t="s">
         <v>15</v>
       </c>
@@ -1388,7 +1416,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15">
       <c r="A5" s="4" t="s">
         <v>17</v>
       </c>
@@ -1435,7 +1463,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15">
       <c r="A6" s="4" t="s">
         <v>18</v>
       </c>
@@ -1468,7 +1496,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15">
       <c r="A7" s="4" t="s">
         <v>19</v>
       </c>
@@ -1497,7 +1525,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15">
       <c r="A8" s="4" t="s">
         <v>20</v>
       </c>
@@ -1532,7 +1560,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15">
       <c r="A9" s="4" t="s">
         <v>21</v>
       </c>
@@ -1543,7 +1571,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15">
       <c r="A10" s="4" t="s">
         <v>22</v>
       </c>
@@ -1584,7 +1612,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15">
       <c r="A11" s="4" t="s">
         <v>23</v>
       </c>
@@ -1615,7 +1643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15">
       <c r="A12" s="4" t="s">
         <v>24</v>
       </c>
@@ -1662,7 +1690,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15">
       <c r="A13" s="4" t="s">
         <v>25</v>
       </c>
@@ -1693,7 +1721,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15">
       <c r="A14" s="4" t="s">
         <v>26</v>
       </c>
@@ -1740,7 +1768,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15">
       <c r="A15" s="4" t="s">
         <v>27</v>
       </c>
@@ -1779,7 +1807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15">
       <c r="A16" s="4" t="s">
         <v>28</v>
       </c>
@@ -1806,7 +1834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:15">
       <c r="A17" s="4" t="s">
         <v>29</v>
       </c>
@@ -1853,7 +1881,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:15">
       <c r="A18" s="4" t="s">
         <v>30</v>
       </c>
@@ -1890,7 +1918,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:15">
       <c r="A19" s="4" t="s">
         <v>31</v>
       </c>
@@ -1937,7 +1965,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:15">
       <c r="A20" s="4" t="s">
         <v>32</v>
       </c>
@@ -1970,7 +1998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:15">
       <c r="A21" s="4" t="s">
         <v>33</v>
       </c>
@@ -1995,7 +2023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:15">
       <c r="A22" s="4" t="s">
         <v>34</v>
       </c>
@@ -2042,7 +2070,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:15">
       <c r="A23" s="4" t="s">
         <v>35</v>
       </c>
@@ -2089,7 +2117,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:15">
       <c r="A24" s="4" t="s">
         <v>36</v>
       </c>
@@ -2134,7 +2162,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:15">
       <c r="A25" s="4" t="s">
         <v>37</v>
       </c>
@@ -2173,7 +2201,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:15">
       <c r="A26" s="4" t="s">
         <v>38</v>
       </c>
@@ -2220,7 +2248,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:15">
       <c r="A27" s="4" t="s">
         <v>39</v>
       </c>
@@ -2267,7 +2295,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:15">
       <c r="A28" s="4" t="s">
         <v>40</v>
       </c>
@@ -2314,7 +2342,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:15">
       <c r="A29" s="4" t="s">
         <v>41</v>
       </c>
@@ -2341,7 +2369,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:15">
       <c r="A30" s="4" t="s">
         <v>42</v>
       </c>
@@ -2366,7 +2394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:15">
       <c r="A31" s="4" t="s">
         <v>43</v>
       </c>
@@ -2401,7 +2429,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:15">
       <c r="A32" s="4" t="s">
         <v>44</v>
       </c>
@@ -2446,7 +2474,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:15">
       <c r="A33" s="4" t="s">
         <v>45</v>
       </c>
@@ -2493,7 +2521,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:15">
       <c r="A34" s="4" t="s">
         <v>46</v>
       </c>
@@ -2540,7 +2568,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:15">
       <c r="A35" s="4" t="s">
         <v>47</v>
       </c>
@@ -2565,7 +2593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:15">
       <c r="A36" s="4" t="s">
         <v>48</v>
       </c>
@@ -2610,7 +2638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:15">
       <c r="A37" s="4" t="s">
         <v>49</v>
       </c>
@@ -2657,7 +2685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:15">
       <c r="A38" s="4" t="s">
         <v>50</v>
       </c>
@@ -2686,7 +2714,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:15">
       <c r="A39" s="4" t="s">
         <v>51</v>
       </c>
@@ -2715,7 +2743,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:15">
       <c r="A40" s="4" t="s">
         <v>52</v>
       </c>
@@ -2746,7 +2774,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:15">
       <c r="A41" s="4" t="s">
         <v>53</v>
       </c>
@@ -2771,7 +2799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:15">
       <c r="A42" s="4" t="s">
         <v>54</v>
       </c>
@@ -2796,7 +2824,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:15">
       <c r="A43" s="4" t="s">
         <v>55</v>
       </c>
@@ -2829,7 +2857,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:15">
       <c r="A44" s="4" t="s">
         <v>56</v>
       </c>
@@ -2862,7 +2890,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:15">
       <c r="A45" s="4" t="s">
         <v>57</v>
       </c>
@@ -2887,7 +2915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:15">
       <c r="A46" s="4" t="s">
         <v>58</v>
       </c>
@@ -2922,7 +2950,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:15">
       <c r="A47" s="4" t="s">
         <v>59</v>
       </c>
@@ -2959,7 +2987,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:15">
       <c r="A48" s="4" t="s">
         <v>60</v>
       </c>
@@ -2994,7 +3022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:15">
       <c r="A49" s="4" t="s">
         <v>61</v>
       </c>
@@ -3023,7 +3051,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:15">
       <c r="A50" s="4" t="s">
         <v>62</v>
       </c>
@@ -3052,7 +3080,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:15">
       <c r="A51" s="4" t="s">
         <v>63</v>
       </c>
@@ -3083,7 +3111,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:15">
       <c r="A52" s="4" t="s">
         <v>64</v>
       </c>
@@ -3110,7 +3138,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:15">
       <c r="A53" s="4" t="s">
         <v>65</v>
       </c>
@@ -3157,7 +3185,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:15">
       <c r="A54" s="4" t="s">
         <v>66</v>
       </c>
@@ -3186,7 +3214,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:15">
       <c r="A55" s="4" t="s">
         <v>67</v>
       </c>
@@ -3211,7 +3239,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:15">
       <c r="A56" s="4" t="s">
         <v>68</v>
       </c>
@@ -3236,7 +3264,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:15">
       <c r="A57" s="4" t="s">
         <v>69</v>
       </c>
@@ -3261,7 +3289,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:15">
       <c r="A58" s="4" t="s">
         <v>70</v>
       </c>
@@ -3286,7 +3314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:15">
       <c r="A59" s="4" t="s">
         <v>71</v>
       </c>
@@ -3311,7 +3339,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:15">
       <c r="A60" s="4" t="s">
         <v>72</v>
       </c>
@@ -3336,7 +3364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:15">
       <c r="A61" s="4" t="s">
         <v>73</v>
       </c>
@@ -3361,7 +3389,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:15">
       <c r="A62" s="4" t="s">
         <v>74</v>
       </c>
@@ -3386,7 +3414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:15">
       <c r="A63" s="4" t="s">
         <v>75</v>
       </c>
@@ -3413,7 +3441,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:15">
       <c r="A64" s="4" t="s">
         <v>76</v>
       </c>
@@ -3424,7 +3452,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:15">
       <c r="A65" s="4" t="s">
         <v>77</v>
       </c>
@@ -3459,7 +3487,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:15">
       <c r="A66" s="4" t="s">
         <v>78</v>
       </c>
@@ -3486,7 +3514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:15">
       <c r="A67" s="4" t="s">
         <v>79</v>
       </c>
@@ -3511,7 +3539,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:15">
       <c r="A68" s="4" t="s">
         <v>80</v>
       </c>
@@ -3536,7 +3564,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:15">
       <c r="A69" s="4" t="s">
         <v>81</v>
       </c>
@@ -3561,7 +3589,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:15">
       <c r="A70" s="4" t="s">
         <v>82</v>
       </c>
@@ -3604,7 +3632,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:15">
       <c r="A71" s="4" t="s">
         <v>83</v>
       </c>
@@ -3651,7 +3679,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:15">
       <c r="A72" s="4" t="s">
         <v>84</v>
       </c>
@@ -3662,7 +3690,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:15">
       <c r="A73" s="4" t="s">
         <v>85</v>
       </c>
@@ -3687,7 +3715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:15">
       <c r="A74" s="4" t="s">
         <v>86</v>
       </c>
@@ -3724,7 +3752,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:15">
       <c r="A75" s="4" t="s">
         <v>87</v>
       </c>
@@ -3753,7 +3781,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:15">
       <c r="A76" s="4" t="s">
         <v>88</v>
       </c>
@@ -3796,7 +3824,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:15">
       <c r="A77" s="4" t="s">
         <v>89</v>
       </c>
@@ -3843,7 +3871,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:15">
       <c r="A78" s="4" t="s">
         <v>90</v>
       </c>
@@ -3888,7 +3916,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:15">
       <c r="A79" s="4" t="s">
         <v>91</v>
       </c>
@@ -3933,7 +3961,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:15">
       <c r="A80" s="4" t="s">
         <v>92</v>
       </c>
@@ -3964,7 +3992,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:15">
       <c r="A81" s="4" t="s">
         <v>93</v>
       </c>
@@ -3993,7 +4021,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:15">
       <c r="A82" s="4" t="s">
         <v>94</v>
       </c>
@@ -4024,7 +4052,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:15">
       <c r="A83" s="4" t="s">
         <v>95</v>
       </c>
@@ -4049,7 +4077,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:15">
       <c r="A84" s="4" t="s">
         <v>95</v>
       </c>
@@ -4060,7 +4088,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:15">
       <c r="A85" s="4" t="s">
         <v>96</v>
       </c>
@@ -4105,7 +4133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:15">
       <c r="A86" s="4" t="s">
         <v>97</v>
       </c>
@@ -4150,7 +4178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:15">
       <c r="A87" s="4" t="s">
         <v>98</v>
       </c>
@@ -4197,7 +4225,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:15">
       <c r="A88" s="4" t="s">
         <v>99</v>
       </c>
@@ -4224,7 +4252,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:15">
       <c r="A89" s="4" t="s">
         <v>100</v>
       </c>
@@ -4251,7 +4279,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:15">
       <c r="A90" s="4" t="s">
         <v>101</v>
       </c>
@@ -4276,7 +4304,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:15">
       <c r="A91" s="4" t="s">
         <v>102</v>
       </c>
@@ -4307,7 +4335,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:15">
       <c r="A92" s="4" t="s">
         <v>103</v>
       </c>
@@ -4334,7 +4362,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:15">
       <c r="A93" s="4" t="s">
         <v>104</v>
       </c>
@@ -4359,7 +4387,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:15">
       <c r="A94" s="4" t="s">
         <v>105</v>
       </c>
@@ -4384,7 +4412,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:15">
       <c r="A95" s="4" t="s">
         <v>106</v>
       </c>
@@ -4409,7 +4437,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:15">
       <c r="A96" s="4" t="s">
         <v>107</v>
       </c>
@@ -4436,7 +4464,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:15">
       <c r="A97" s="4" t="s">
         <v>108</v>
       </c>
@@ -4447,7 +4475,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:15">
       <c r="A98" s="4" t="s">
         <v>109</v>
       </c>
@@ -4472,7 +4500,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:15">
       <c r="A99" s="4" t="s">
         <v>109</v>
       </c>
@@ -4483,7 +4511,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:15">
       <c r="A100" s="4" t="s">
         <v>110</v>
       </c>
@@ -4510,7 +4538,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:15">
       <c r="A101" s="4" t="s">
         <v>110</v>
       </c>
@@ -4521,7 +4549,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="102" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:15">
       <c r="A102" s="4" t="s">
         <v>111</v>
       </c>
@@ -4552,7 +4580,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:15">
       <c r="A103" s="4" t="s">
         <v>112</v>
       </c>
@@ -4579,7 +4607,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:15">
       <c r="A104" s="4" t="s">
         <v>113</v>
       </c>
@@ -4612,7 +4640,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="105" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:15">
       <c r="A105" s="4" t="s">
         <v>114</v>
       </c>
@@ -4639,7 +4667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:15">
       <c r="A106" s="4" t="s">
         <v>115</v>
       </c>
@@ -4664,7 +4692,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:15">
       <c r="A107" s="4" t="s">
         <v>116</v>
       </c>
@@ -4689,7 +4717,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:15">
       <c r="A108" s="4" t="s">
         <v>117</v>
       </c>
@@ -4716,7 +4744,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:15">
       <c r="A109" s="4" t="s">
         <v>118</v>
       </c>
@@ -4741,7 +4769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:15">
       <c r="A110" s="4" t="s">
         <v>119</v>
       </c>
@@ -4766,7 +4794,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:15">
       <c r="A111" s="4" t="s">
         <v>120</v>
       </c>
@@ -4797,7 +4825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:15">
       <c r="A112" s="4" t="s">
         <v>121</v>
       </c>
@@ -4822,7 +4850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:15">
       <c r="A113" s="4" t="s">
         <v>122</v>
       </c>
@@ -4851,7 +4879,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="114" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:15">
       <c r="A114" s="4" t="s">
         <v>123</v>
       </c>
@@ -4876,7 +4904,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:15">
       <c r="A115" s="4" t="s">
         <v>124</v>
       </c>
@@ -4887,7 +4915,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="116" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:15">
       <c r="A116" s="4" t="s">
         <v>125</v>
       </c>
@@ -4916,7 +4944,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="117" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:15">
       <c r="A117" s="4" t="s">
         <v>126</v>
       </c>
@@ -4943,7 +4971,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="118" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:15">
       <c r="A118" s="4" t="s">
         <v>126</v>
       </c>
@@ -4954,7 +4982,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="119" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:15">
       <c r="A119" s="4" t="s">
         <v>127</v>
       </c>
@@ -4979,7 +5007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:15">
       <c r="A120" s="4" t="s">
         <v>128</v>
       </c>
@@ -5006,7 +5034,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:15">
       <c r="A121" s="4" t="s">
         <v>128</v>
       </c>
@@ -5017,7 +5045,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:15">
       <c r="A122" s="4" t="s">
         <v>129</v>
       </c>
@@ -5044,7 +5072,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:15">
       <c r="A123" s="4" t="s">
         <v>130</v>
       </c>
@@ -5055,7 +5083,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="124" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:15">
       <c r="A124" s="4" t="s">
         <v>131</v>
       </c>
@@ -5084,7 +5112,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:15">
       <c r="A125" s="4" t="s">
         <v>132</v>
       </c>
@@ -5109,7 +5137,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:15">
       <c r="A126" s="4" t="s">
         <v>133</v>
       </c>
@@ -5138,7 +5166,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="127" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:15">
       <c r="A127" s="4" t="s">
         <v>134</v>
       </c>
@@ -5165,7 +5193,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="128" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:15">
       <c r="A128" s="4" t="s">
         <v>134</v>
       </c>
@@ -5176,7 +5204,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="129" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:15">
       <c r="A129" s="4" t="s">
         <v>135</v>
       </c>
@@ -5201,7 +5229,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="130" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:15">
       <c r="A130" s="4" t="s">
         <v>135</v>
       </c>
@@ -5212,7 +5240,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="131" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:15">
       <c r="A131" s="4" t="s">
         <v>136</v>
       </c>
@@ -5237,7 +5265,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:15">
       <c r="A132" s="4" t="s">
         <v>137</v>
       </c>
@@ -5270,7 +5298,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:15">
       <c r="A133" s="4" t="s">
         <v>138</v>
       </c>
@@ -5281,7 +5309,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:15">
       <c r="A134" s="4" t="s">
         <v>139</v>
       </c>
@@ -5312,7 +5340,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="135" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:15">
       <c r="A135" s="4" t="s">
         <v>139</v>
       </c>
@@ -5323,7 +5351,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="136" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:15">
       <c r="A136" s="4" t="s">
         <v>140</v>
       </c>
@@ -5350,7 +5378,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:15">
       <c r="A137" s="4" t="s">
         <v>141</v>
       </c>
@@ -5375,7 +5403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:15">
       <c r="A138" s="4" t="s">
         <v>142</v>
       </c>
@@ -5402,7 +5430,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:15">
       <c r="A139" s="4" t="s">
         <v>143</v>
       </c>
@@ -5427,7 +5455,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="140" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:15">
       <c r="A140" s="4" t="s">
         <v>143</v>
       </c>
@@ -5438,7 +5466,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="141" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:15">
       <c r="A141" s="4" t="s">
         <v>144</v>
       </c>
@@ -5465,7 +5493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:15">
       <c r="A142" s="4" t="s">
         <v>145</v>
       </c>
@@ -5476,7 +5504,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="143" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:15">
       <c r="A143" s="4" t="s">
         <v>146</v>
       </c>
@@ -5503,7 +5531,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:15">
       <c r="A144" s="4" t="s">
         <v>147</v>
       </c>
@@ -5548,7 +5576,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:15">
       <c r="A145" s="4" t="s">
         <v>148</v>
       </c>
@@ -5573,7 +5601,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:15">
       <c r="A146" s="4" t="s">
         <v>149</v>
       </c>
@@ -5584,7 +5612,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:15">
       <c r="A147" s="4" t="s">
         <v>150</v>
       </c>
@@ -5609,7 +5637,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:15">
       <c r="A148" s="4" t="s">
         <v>150</v>
       </c>
@@ -5620,7 +5648,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:15">
       <c r="A149" s="4" t="s">
         <v>151</v>
       </c>
@@ -5649,7 +5677,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:15">
       <c r="A150" s="4" t="s">
         <v>151</v>
       </c>
@@ -5660,7 +5688,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:15">
       <c r="A151" s="4" t="s">
         <v>152</v>
       </c>
@@ -5687,7 +5715,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:15">
       <c r="A152" s="4" t="s">
         <v>152</v>
       </c>
@@ -5698,7 +5726,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:15">
       <c r="A153" s="4" t="s">
         <v>153</v>
       </c>
@@ -5733,7 +5761,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:15">
       <c r="A154" s="4" t="s">
         <v>154</v>
       </c>
@@ -5760,7 +5788,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:15">
       <c r="A155" s="4" t="s">
         <v>155</v>
       </c>
@@ -5793,7 +5821,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:15">
       <c r="A156" s="4" t="s">
         <v>156</v>
       </c>
@@ -5822,7 +5850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:15">
       <c r="A157" s="4" t="s">
         <v>157</v>
       </c>
@@ -5861,7 +5889,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:15">
       <c r="A158" s="4" t="s">
         <v>158</v>
       </c>
@@ -5872,7 +5900,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:15">
       <c r="A159" s="4" t="s">
         <v>159</v>
       </c>
@@ -5883,7 +5911,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="160" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:15">
       <c r="A160" s="4" t="s">
         <v>160</v>
       </c>
@@ -5910,7 +5938,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="161" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:15">
       <c r="A161" s="4" t="s">
         <v>161</v>
       </c>
@@ -5935,7 +5963,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="162" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:15">
       <c r="A162" s="4" t="s">
         <v>161</v>
       </c>
@@ -5946,7 +5974,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="163" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:15">
       <c r="A163" s="4" t="s">
         <v>162</v>
       </c>
@@ -5977,7 +6005,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:15">
       <c r="A164" s="4" t="s">
         <v>163</v>
       </c>
@@ -6002,7 +6030,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="165" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:15">
       <c r="A165" s="4" t="s">
         <v>163</v>
       </c>
@@ -6013,7 +6041,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="166" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:15">
       <c r="A166" s="4" t="s">
         <v>164</v>
       </c>
@@ -6038,7 +6066,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:15">
       <c r="A167" s="4" t="s">
         <v>165</v>
       </c>
@@ -6063,7 +6091,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:15">
       <c r="A168" s="4" t="s">
         <v>166</v>
       </c>
@@ -6088,7 +6116,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:15">
       <c r="A169" s="4" t="s">
         <v>167</v>
       </c>
@@ -6115,7 +6143,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:15">
       <c r="A170" s="4" t="s">
         <v>168</v>
       </c>
@@ -6142,7 +6170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:15">
       <c r="A171" s="4" t="s">
         <v>169</v>
       </c>
@@ -6171,7 +6199,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:15">
       <c r="A172" s="4" t="s">
         <v>170</v>
       </c>
@@ -6202,7 +6230,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:15">
       <c r="A173" s="4" t="s">
         <v>171</v>
       </c>
@@ -6213,7 +6241,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="174" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:15">
       <c r="A174" s="4" t="s">
         <v>172</v>
       </c>
@@ -6238,7 +6266,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:15">
       <c r="A175" s="4" t="s">
         <v>173</v>
       </c>
@@ -6263,7 +6291,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:15">
       <c r="A176" s="4" t="s">
         <v>174</v>
       </c>
@@ -6288,7 +6316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:15">
       <c r="A177" s="4" t="s">
         <v>175</v>
       </c>
@@ -6299,7 +6327,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="178" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:15">
       <c r="A178" s="4" t="s">
         <v>176</v>
       </c>
@@ -6324,7 +6352,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:15">
       <c r="A179" s="4" t="s">
         <v>177</v>
       </c>
@@ -6349,7 +6377,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:15">
       <c r="A180" s="4" t="s">
         <v>178</v>
       </c>
@@ -6360,7 +6388,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="181" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:15">
       <c r="A181" s="4" t="s">
         <v>179</v>
       </c>
@@ -6389,7 +6417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:15">
       <c r="A182" s="4" t="s">
         <v>180</v>
       </c>
@@ -6416,7 +6444,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:15">
       <c r="A183" s="4" t="s">
         <v>181</v>
       </c>
@@ -6441,7 +6469,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:15">
       <c r="A184" s="4" t="s">
         <v>182</v>
       </c>
@@ -6468,7 +6496,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:15">
       <c r="A185" s="4" t="s">
         <v>183</v>
       </c>
@@ -6493,7 +6521,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:15">
       <c r="A186" s="4" t="s">
         <v>184</v>
       </c>
@@ -6518,7 +6546,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:15">
       <c r="A187" s="4" t="s">
         <v>185</v>
       </c>
@@ -6529,7 +6557,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="188" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:15">
       <c r="A188" s="4" t="s">
         <v>186</v>
       </c>
@@ -6554,7 +6582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:15">
       <c r="A189" s="4" t="s">
         <v>187</v>
       </c>
@@ -6565,7 +6593,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="190" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:15">
       <c r="A190" s="4" t="s">
         <v>188</v>
       </c>
@@ -6576,7 +6604,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="191" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:15">
       <c r="A191" s="4" t="s">
         <v>189</v>
       </c>
@@ -6607,7 +6635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:15">
       <c r="A192" s="4" t="s">
         <v>190</v>
       </c>
@@ -6634,7 +6662,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="193" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:15">
       <c r="A193" s="4" t="s">
         <v>190</v>
       </c>
@@ -6645,7 +6673,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="194" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:15">
       <c r="A194" s="4" t="s">
         <v>191</v>
       </c>
@@ -6684,7 +6712,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="195" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:15">
       <c r="A195" s="4" t="s">
         <v>192</v>
       </c>
@@ -6715,7 +6743,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="196" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:15">
       <c r="A196" s="4" t="s">
         <v>192</v>
       </c>
@@ -6726,7 +6754,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="197" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:15">
       <c r="A197" s="4" t="s">
         <v>193</v>
       </c>
@@ -6753,7 +6781,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="198" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:15">
       <c r="A198" s="4" t="s">
         <v>193</v>
       </c>
@@ -6764,7 +6792,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="199" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:15">
       <c r="A199" s="4" t="s">
         <v>194</v>
       </c>
@@ -6775,7 +6803,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="200" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:15">
       <c r="A200" s="4" t="s">
         <v>195</v>
       </c>
@@ -6800,7 +6828,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="201" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:15">
       <c r="A201" s="4" t="s">
         <v>195</v>
       </c>
@@ -6811,7 +6839,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="202" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:15">
       <c r="A202" s="4" t="s">
         <v>196</v>
       </c>
@@ -6836,7 +6864,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="203" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:15">
       <c r="A203" s="4" t="s">
         <v>196</v>
       </c>
@@ -6847,7 +6875,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="204" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:15">
       <c r="A204" s="4" t="s">
         <v>197</v>
       </c>
@@ -6858,7 +6886,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="205" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:15">
       <c r="A205" s="4" t="s">
         <v>198</v>
       </c>
@@ -6885,7 +6913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:15">
       <c r="A206" s="4" t="s">
         <v>199</v>
       </c>
@@ -6912,7 +6940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:15">
       <c r="A207" s="4" t="s">
         <v>200</v>
       </c>
@@ -6939,7 +6967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:15">
       <c r="A208" s="4" t="s">
         <v>201</v>
       </c>
@@ -6974,7 +7002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:15">
       <c r="A209" s="4" t="s">
         <v>202</v>
       </c>
@@ -6999,7 +7027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="210" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:15">
       <c r="A210" s="4" t="s">
         <v>203</v>
       </c>
@@ -7034,7 +7062,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="211" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:15">
       <c r="A211" s="4" t="s">
         <v>204</v>
       </c>
@@ -7063,7 +7091,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:15">
       <c r="A212" s="4" t="s">
         <v>205</v>
       </c>
@@ -7074,7 +7102,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="213" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:15">
       <c r="A213" s="4" t="s">
         <v>206</v>
       </c>
@@ -7099,7 +7127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:15">
       <c r="A214" s="4" t="s">
         <v>207</v>
       </c>
@@ -7110,7 +7138,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="215" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:15">
       <c r="A215" s="4" t="s">
         <v>208</v>
       </c>
@@ -7157,7 +7185,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="216" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:15">
       <c r="A216" s="4" t="s">
         <v>209</v>
       </c>
@@ -7198,7 +7226,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="217" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:15">
       <c r="A217" s="4" t="s">
         <v>210</v>
       </c>
@@ -7235,7 +7263,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:15">
       <c r="A218" s="4" t="s">
         <v>211</v>
       </c>
@@ -7260,7 +7288,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:15">
       <c r="A219" s="6" t="s">
         <v>212</v>
       </c>
@@ -7271,7 +7299,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="220" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:15">
       <c r="A220" s="6" t="s">
         <v>213</v>
       </c>
@@ -7300,7 +7328,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="221" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:15">
       <c r="A221" s="6" t="s">
         <v>214</v>
       </c>
@@ -7327,7 +7355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:15">
       <c r="A222" s="6" t="s">
         <v>215</v>
       </c>
@@ -7338,7 +7366,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="223" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:15">
       <c r="A223" s="6" t="s">
         <v>216</v>
       </c>
@@ -7349,7 +7377,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="224" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:15">
       <c r="A224" s="6" t="s">
         <v>217</v>
       </c>
@@ -7360,7 +7388,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="225" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:15">
       <c r="A225" s="6" t="s">
         <v>218</v>
       </c>
@@ -7385,7 +7413,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:15">
       <c r="A226" s="6" t="s">
         <v>219</v>
       </c>
@@ -7414,7 +7442,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="227" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:15">
       <c r="A227" s="6" t="s">
         <v>220</v>
       </c>
@@ -7425,7 +7453,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="228" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:15">
       <c r="A228" s="6" t="s">
         <v>221</v>
       </c>
@@ -7450,7 +7478,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="229" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:15">
       <c r="A229" s="6" t="s">
         <v>222</v>
       </c>
@@ -7477,7 +7505,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="230" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:15">
       <c r="A230" s="6" t="s">
         <v>223</v>
       </c>
@@ -7502,7 +7530,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="231" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:15">
       <c r="A231" s="6" t="s">
         <v>224</v>
       </c>
@@ -7529,7 +7557,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="232" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:15">
       <c r="A232" s="6" t="s">
         <v>225</v>
       </c>
@@ -7562,7 +7590,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="233" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:15">
       <c r="A233" s="6" t="s">
         <v>226</v>
       </c>
@@ -7587,7 +7615,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="234" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:15">
       <c r="A234" s="6" t="s">
         <v>227</v>
       </c>
@@ -7598,7 +7626,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="235" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:15">
       <c r="A235" s="6" t="s">
         <v>228</v>
       </c>
@@ -7625,7 +7653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="236" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:15">
       <c r="A236" s="6" t="s">
         <v>229</v>
       </c>
@@ -7650,7 +7678,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="237" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:15">
       <c r="A237" s="6" t="s">
         <v>229</v>
       </c>
@@ -7661,7 +7689,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="238" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:15">
       <c r="A238" s="6" t="s">
         <v>230</v>
       </c>
@@ -7686,7 +7714,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="239" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:15">
       <c r="A239" s="6" t="s">
         <v>230</v>
       </c>
@@ -7697,7 +7725,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="240" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:15">
       <c r="A240" s="6" t="s">
         <v>231</v>
       </c>
@@ -7724,7 +7752,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="241" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:15">
       <c r="A241" s="6" t="s">
         <v>232</v>
       </c>
@@ -7751,7 +7779,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="242" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:15">
       <c r="A242" s="6" t="s">
         <v>233</v>
       </c>
@@ -7776,7 +7804,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="243" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:15">
       <c r="A243" s="6" t="s">
         <v>234</v>
       </c>
@@ -7813,7 +7841,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="244" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:15">
       <c r="A244" s="6" t="s">
         <v>235</v>
       </c>
@@ -7824,7 +7852,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="245" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:15">
       <c r="A245" s="6" t="s">
         <v>236</v>
       </c>
@@ -7835,7 +7863,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="246" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:15">
       <c r="A246" s="6" t="s">
         <v>237</v>
       </c>
@@ -7860,7 +7888,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="247" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:15">
       <c r="A247" s="6" t="s">
         <v>238</v>
       </c>
@@ -7907,7 +7935,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="248" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:15">
       <c r="A248" s="6" t="s">
         <v>239</v>
       </c>
@@ -7936,7 +7964,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="249" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:15">
       <c r="A249" s="6" t="s">
         <v>240</v>
       </c>
@@ -7961,7 +7989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="250" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:15">
       <c r="A250" s="6" t="s">
         <v>241</v>
       </c>
@@ -7986,7 +8014,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="251" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:15">
       <c r="A251" s="6" t="s">
         <v>241</v>
       </c>
@@ -7997,7 +8025,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="252" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:15">
       <c r="A252" s="6" t="s">
         <v>242</v>
       </c>
@@ -8022,7 +8050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="253" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:15">
       <c r="A253" s="6" t="s">
         <v>243</v>
       </c>
@@ -8053,7 +8081,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="254" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:15">
       <c r="A254" s="6" t="s">
         <v>244</v>
       </c>
@@ -8082,7 +8110,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="255" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:15">
       <c r="A255" s="6" t="s">
         <v>245</v>
       </c>
@@ -8109,7 +8137,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="256" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:15">
       <c r="A256" s="6" t="s">
         <v>246</v>
       </c>
@@ -8136,7 +8164,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="257" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:15">
       <c r="A257" s="6" t="s">
         <v>247</v>
       </c>
@@ -8163,7 +8191,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="258" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:15">
       <c r="A258" s="6" t="s">
         <v>247</v>
       </c>
@@ -8174,7 +8202,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="259" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:15">
       <c r="A259" s="6" t="s">
         <v>248</v>
       </c>
@@ -8199,7 +8227,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="260" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:15">
       <c r="A260" s="6" t="s">
         <v>248</v>
       </c>
@@ -8210,7 +8238,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="261" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:15">
       <c r="A261" s="6" t="s">
         <v>249</v>
       </c>
@@ -8237,7 +8265,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="262" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:15">
       <c r="A262" s="6" t="s">
         <v>250</v>
       </c>
@@ -8272,7 +8300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="263" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:15">
       <c r="A263" s="6" t="s">
         <v>251</v>
       </c>
@@ -8297,7 +8325,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="264" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:15">
       <c r="A264" s="6" t="s">
         <v>252</v>
       </c>
@@ -8322,7 +8350,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="265" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:15">
       <c r="A265" s="6" t="s">
         <v>252</v>
       </c>
@@ -8333,7 +8361,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="266" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:15">
       <c r="A266" s="6" t="s">
         <v>253</v>
       </c>
@@ -8360,7 +8388,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="267" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:15">
       <c r="A267" s="6" t="s">
         <v>254</v>
       </c>
@@ -8385,7 +8413,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="268" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:15">
       <c r="A268" s="6" t="s">
         <v>255</v>
       </c>
@@ -8414,7 +8442,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="269" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:15">
       <c r="A269" s="6" t="s">
         <v>256</v>
       </c>
@@ -8439,7 +8467,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="270" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:15">
       <c r="A270" s="6" t="s">
         <v>257</v>
       </c>
@@ -8464,7 +8492,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="271" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:15">
       <c r="A271" s="6" t="s">
         <v>258</v>
       </c>
@@ -8489,7 +8517,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="272" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:15">
       <c r="A272" s="6" t="s">
         <v>258</v>
       </c>
@@ -8500,7 +8528,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="273" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:15">
       <c r="A273" s="6" t="s">
         <v>259</v>
       </c>
@@ -8525,7 +8553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="274" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:15">
       <c r="A274" s="6" t="s">
         <v>260</v>
       </c>
@@ -8535,6 +8563,882 @@
       <c r="O274">
         <v>3</v>
       </c>
+    </row>
+    <row r="275" spans="1:15">
+      <c r="A275" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="B275" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="C275" s="9">
+        <v>96</v>
+      </c>
+      <c r="D275" s="9">
+        <v>111</v>
+      </c>
+      <c r="E275" s="9">
+        <v>151</v>
+      </c>
+      <c r="F275" s="9">
+        <v>138</v>
+      </c>
+      <c r="G275" s="9">
+        <v>418</v>
+      </c>
+      <c r="H275" s="9">
+        <v>171</v>
+      </c>
+      <c r="I275" s="9">
+        <v>327</v>
+      </c>
+      <c r="J275" s="9">
+        <v>167</v>
+      </c>
+      <c r="K275" s="9">
+        <v>193</v>
+      </c>
+      <c r="L275" s="9">
+        <v>321</v>
+      </c>
+      <c r="M275" s="9">
+        <v>119</v>
+      </c>
+      <c r="N275" s="9">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="276" spans="1:15">
+      <c r="A276" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="B276" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="C276" s="9">
+        <v>92</v>
+      </c>
+      <c r="D276" s="9">
+        <v>40</v>
+      </c>
+      <c r="E276" s="9">
+        <v>158</v>
+      </c>
+      <c r="F276" s="9">
+        <v>193</v>
+      </c>
+      <c r="G276" s="9">
+        <v>284</v>
+      </c>
+      <c r="H276" s="9">
+        <v>180</v>
+      </c>
+      <c r="I276" s="9">
+        <v>171</v>
+      </c>
+      <c r="J276" s="9">
+        <v>89</v>
+      </c>
+      <c r="K276" s="9">
+        <v>178</v>
+      </c>
+      <c r="L276" s="9">
+        <v>271</v>
+      </c>
+      <c r="M276" s="9">
+        <v>119</v>
+      </c>
+      <c r="N276" s="9">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="277" spans="1:15">
+      <c r="A277" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="B277" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="C277" s="9">
+        <v>23</v>
+      </c>
+      <c r="D277" s="9">
+        <v>7</v>
+      </c>
+      <c r="E277" s="9">
+        <v>51</v>
+      </c>
+      <c r="F277" s="9">
+        <v>93</v>
+      </c>
+      <c r="G277" s="9">
+        <v>136</v>
+      </c>
+      <c r="H277" s="9">
+        <v>85</v>
+      </c>
+      <c r="I277" s="9">
+        <v>78</v>
+      </c>
+      <c r="J277" s="9">
+        <v>91</v>
+      </c>
+      <c r="K277" s="9">
+        <v>88</v>
+      </c>
+      <c r="L277" s="9">
+        <v>123</v>
+      </c>
+      <c r="M277" s="9">
+        <v>70</v>
+      </c>
+      <c r="N277" s="9">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="278" spans="1:15">
+      <c r="A278" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="B278" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="C278" s="9">
+        <v>53</v>
+      </c>
+      <c r="D278" s="9">
+        <v>16</v>
+      </c>
+      <c r="E278" s="9">
+        <v>37</v>
+      </c>
+      <c r="F278" s="9">
+        <v>93</v>
+      </c>
+      <c r="G278" s="9">
+        <v>135</v>
+      </c>
+      <c r="H278" s="9">
+        <v>9</v>
+      </c>
+      <c r="I278" s="9">
+        <v>111</v>
+      </c>
+      <c r="J278" s="9">
+        <v>90</v>
+      </c>
+      <c r="K278" s="9">
+        <v>57</v>
+      </c>
+      <c r="L278" s="9">
+        <v>129</v>
+      </c>
+      <c r="M278" s="9">
+        <v>37</v>
+      </c>
+      <c r="N278" s="9">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="279" spans="1:15">
+      <c r="A279" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="B279" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="C279" s="9">
+        <v>29</v>
+      </c>
+      <c r="D279" s="9">
+        <v>18</v>
+      </c>
+      <c r="E279" s="9">
+        <v>31</v>
+      </c>
+      <c r="F279" s="9">
+        <v>41</v>
+      </c>
+      <c r="G279" s="9">
+        <v>59</v>
+      </c>
+      <c r="H279" s="9">
+        <v>46</v>
+      </c>
+      <c r="I279" s="9">
+        <v>52</v>
+      </c>
+      <c r="J279" s="9">
+        <v>44</v>
+      </c>
+      <c r="K279" s="9">
+        <v>44</v>
+      </c>
+      <c r="L279" s="9">
+        <v>65</v>
+      </c>
+      <c r="M279" s="9">
+        <v>24</v>
+      </c>
+      <c r="N279" s="9">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="280" spans="1:15">
+      <c r="A280" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="B280" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="C280" s="9">
+        <v>26</v>
+      </c>
+      <c r="D280" s="9"/>
+      <c r="E280" s="9">
+        <v>8</v>
+      </c>
+      <c r="F280" s="9">
+        <v>54</v>
+      </c>
+      <c r="G280" s="9">
+        <v>29</v>
+      </c>
+      <c r="H280" s="9">
+        <v>29</v>
+      </c>
+      <c r="I280" s="9">
+        <v>18</v>
+      </c>
+      <c r="J280" s="9">
+        <v>54</v>
+      </c>
+      <c r="K280" s="9">
+        <v>117</v>
+      </c>
+      <c r="L280" s="9">
+        <v>67</v>
+      </c>
+      <c r="M280" s="9">
+        <v>8</v>
+      </c>
+      <c r="N280" s="9">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="281" spans="1:15">
+      <c r="A281" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="B281" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="C281" s="9">
+        <v>12</v>
+      </c>
+      <c r="D281" s="9">
+        <v>4</v>
+      </c>
+      <c r="E281" s="9">
+        <v>32</v>
+      </c>
+      <c r="F281" s="9">
+        <v>36</v>
+      </c>
+      <c r="G281" s="9">
+        <v>60</v>
+      </c>
+      <c r="H281" s="9">
+        <v>36</v>
+      </c>
+      <c r="I281" s="9">
+        <v>45</v>
+      </c>
+      <c r="J281" s="9">
+        <v>34</v>
+      </c>
+      <c r="K281" s="9">
+        <v>43</v>
+      </c>
+      <c r="L281" s="9">
+        <v>52</v>
+      </c>
+      <c r="M281" s="9">
+        <v>28</v>
+      </c>
+      <c r="N281" s="9">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="282" spans="1:15">
+      <c r="A282" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="B282" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="C282" s="9">
+        <v>17</v>
+      </c>
+      <c r="D282" s="9">
+        <v>6</v>
+      </c>
+      <c r="E282" s="9">
+        <v>3</v>
+      </c>
+      <c r="F282" s="9">
+        <v>50</v>
+      </c>
+      <c r="G282" s="9">
+        <v>46</v>
+      </c>
+      <c r="H282" s="9">
+        <v>45</v>
+      </c>
+      <c r="I282" s="9">
+        <v>8</v>
+      </c>
+      <c r="J282" s="9">
+        <v>26</v>
+      </c>
+      <c r="K282" s="9">
+        <v>35</v>
+      </c>
+      <c r="L282" s="9">
+        <v>41</v>
+      </c>
+      <c r="M282" s="9">
+        <v>23</v>
+      </c>
+      <c r="N282" s="9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="283" spans="1:15">
+      <c r="A283" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="B283" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="C283" s="9"/>
+      <c r="D283" s="9"/>
+      <c r="E283" s="9"/>
+      <c r="F283" s="9"/>
+      <c r="G283" s="9"/>
+      <c r="H283" s="9"/>
+      <c r="I283" s="9"/>
+      <c r="J283" s="9"/>
+      <c r="K283" s="9"/>
+      <c r="L283" s="9"/>
+      <c r="M283" s="9">
+        <v>2</v>
+      </c>
+      <c r="N283" s="9"/>
+    </row>
+    <row r="284" spans="1:15">
+      <c r="A284" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="B284" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="C284" s="9"/>
+      <c r="D284" s="9"/>
+      <c r="E284" s="9"/>
+      <c r="F284" s="9"/>
+      <c r="G284" s="9"/>
+      <c r="H284" s="9"/>
+      <c r="I284" s="9"/>
+      <c r="J284" s="9"/>
+      <c r="K284" s="9"/>
+      <c r="L284" s="9"/>
+      <c r="M284" s="9">
+        <v>2</v>
+      </c>
+      <c r="N284" s="9"/>
+    </row>
+    <row r="285" spans="1:15">
+      <c r="A285" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="B285" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="C285" s="9"/>
+      <c r="D285" s="9"/>
+      <c r="E285" s="9"/>
+      <c r="F285" s="9"/>
+      <c r="G285" s="9"/>
+      <c r="H285" s="9"/>
+      <c r="I285" s="9"/>
+      <c r="J285" s="9"/>
+      <c r="K285" s="9"/>
+      <c r="L285" s="9"/>
+      <c r="M285" s="9">
+        <v>2</v>
+      </c>
+      <c r="N285" s="9"/>
+    </row>
+    <row r="286" spans="1:15">
+      <c r="A286" s="8" t="s">
+        <v>268</v>
+      </c>
+      <c r="B286" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="C286" s="9"/>
+      <c r="D286" s="9"/>
+      <c r="E286" s="9"/>
+      <c r="F286" s="9"/>
+      <c r="G286" s="9"/>
+      <c r="H286" s="9"/>
+      <c r="I286" s="9"/>
+      <c r="J286" s="9"/>
+      <c r="K286" s="9"/>
+      <c r="L286" s="9"/>
+      <c r="M286" s="9">
+        <v>2</v>
+      </c>
+      <c r="N286" s="9"/>
+    </row>
+    <row r="287" spans="1:15">
+      <c r="A287" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="B287" t="s">
+        <v>265</v>
+      </c>
+      <c r="C287" s="5">
+        <v>96</v>
+      </c>
+      <c r="D287" s="5">
+        <v>111</v>
+      </c>
+      <c r="E287" s="5">
+        <v>151</v>
+      </c>
+      <c r="F287" s="5">
+        <v>138</v>
+      </c>
+      <c r="G287" s="5">
+        <v>418</v>
+      </c>
+      <c r="H287" s="5">
+        <v>171</v>
+      </c>
+      <c r="I287" s="5">
+        <v>327</v>
+      </c>
+      <c r="J287" s="5">
+        <v>167</v>
+      </c>
+      <c r="K287" s="5">
+        <v>193</v>
+      </c>
+      <c r="L287" s="5">
+        <v>321</v>
+      </c>
+      <c r="M287" s="5">
+        <v>119</v>
+      </c>
+      <c r="N287" s="5">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="288" spans="1:15">
+      <c r="A288" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="B288" t="s">
+        <v>265</v>
+      </c>
+      <c r="C288" s="5">
+        <v>92</v>
+      </c>
+      <c r="D288" s="5">
+        <v>40</v>
+      </c>
+      <c r="E288" s="5">
+        <v>158</v>
+      </c>
+      <c r="F288" s="5">
+        <v>193</v>
+      </c>
+      <c r="G288" s="5">
+        <v>284</v>
+      </c>
+      <c r="H288" s="5">
+        <v>180</v>
+      </c>
+      <c r="I288" s="5">
+        <v>171</v>
+      </c>
+      <c r="J288" s="5">
+        <v>89</v>
+      </c>
+      <c r="K288" s="5">
+        <v>178</v>
+      </c>
+      <c r="L288" s="5">
+        <v>271</v>
+      </c>
+      <c r="M288" s="5">
+        <v>119</v>
+      </c>
+      <c r="N288" s="5">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="289" spans="1:14">
+      <c r="A289" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="B289" t="s">
+        <v>265</v>
+      </c>
+      <c r="C289" s="5">
+        <v>23</v>
+      </c>
+      <c r="D289" s="5">
+        <v>7</v>
+      </c>
+      <c r="E289" s="5">
+        <v>51</v>
+      </c>
+      <c r="F289" s="5">
+        <v>93</v>
+      </c>
+      <c r="G289" s="5">
+        <v>136</v>
+      </c>
+      <c r="H289" s="5">
+        <v>85</v>
+      </c>
+      <c r="I289" s="5">
+        <v>78</v>
+      </c>
+      <c r="J289" s="5">
+        <v>91</v>
+      </c>
+      <c r="K289" s="5">
+        <v>88</v>
+      </c>
+      <c r="L289" s="5">
+        <v>123</v>
+      </c>
+      <c r="M289" s="5">
+        <v>70</v>
+      </c>
+      <c r="N289" s="5">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="290" spans="1:14">
+      <c r="A290" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="B290" t="s">
+        <v>265</v>
+      </c>
+      <c r="C290" s="5">
+        <v>53</v>
+      </c>
+      <c r="D290" s="5">
+        <v>16</v>
+      </c>
+      <c r="E290" s="5">
+        <v>37</v>
+      </c>
+      <c r="F290" s="5">
+        <v>93</v>
+      </c>
+      <c r="G290" s="5">
+        <v>135</v>
+      </c>
+      <c r="H290" s="5">
+        <v>9</v>
+      </c>
+      <c r="I290" s="5">
+        <v>111</v>
+      </c>
+      <c r="J290" s="5">
+        <v>90</v>
+      </c>
+      <c r="K290" s="5">
+        <v>57</v>
+      </c>
+      <c r="L290" s="5">
+        <v>129</v>
+      </c>
+      <c r="M290" s="5">
+        <v>37</v>
+      </c>
+      <c r="N290" s="5">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="291" spans="1:14">
+      <c r="A291" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="B291" t="s">
+        <v>265</v>
+      </c>
+      <c r="C291" s="5">
+        <v>29</v>
+      </c>
+      <c r="D291" s="5">
+        <v>18</v>
+      </c>
+      <c r="E291" s="5">
+        <v>31</v>
+      </c>
+      <c r="F291" s="5">
+        <v>41</v>
+      </c>
+      <c r="G291" s="5">
+        <v>59</v>
+      </c>
+      <c r="H291" s="5">
+        <v>46</v>
+      </c>
+      <c r="I291" s="5">
+        <v>52</v>
+      </c>
+      <c r="J291" s="5">
+        <v>44</v>
+      </c>
+      <c r="K291" s="5">
+        <v>44</v>
+      </c>
+      <c r="L291" s="5">
+        <v>65</v>
+      </c>
+      <c r="M291" s="5">
+        <v>24</v>
+      </c>
+      <c r="N291" s="5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="292" spans="1:14">
+      <c r="A292" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="B292" t="s">
+        <v>265</v>
+      </c>
+      <c r="C292" s="5">
+        <v>26</v>
+      </c>
+      <c r="D292" s="5"/>
+      <c r="E292" s="5">
+        <v>8</v>
+      </c>
+      <c r="F292" s="5">
+        <v>54</v>
+      </c>
+      <c r="G292" s="5">
+        <v>29</v>
+      </c>
+      <c r="H292" s="5">
+        <v>29</v>
+      </c>
+      <c r="I292" s="5">
+        <v>18</v>
+      </c>
+      <c r="J292" s="5">
+        <v>54</v>
+      </c>
+      <c r="K292" s="5">
+        <v>117</v>
+      </c>
+      <c r="L292" s="5">
+        <v>67</v>
+      </c>
+      <c r="M292" s="5">
+        <v>8</v>
+      </c>
+      <c r="N292" s="5">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="293" spans="1:14">
+      <c r="A293" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="B293" t="s">
+        <v>265</v>
+      </c>
+      <c r="C293" s="5">
+        <v>12</v>
+      </c>
+      <c r="D293" s="5">
+        <v>4</v>
+      </c>
+      <c r="E293" s="5">
+        <v>32</v>
+      </c>
+      <c r="F293" s="5">
+        <v>36</v>
+      </c>
+      <c r="G293" s="5">
+        <v>60</v>
+      </c>
+      <c r="H293" s="5">
+        <v>36</v>
+      </c>
+      <c r="I293" s="5">
+        <v>45</v>
+      </c>
+      <c r="J293" s="5">
+        <v>34</v>
+      </c>
+      <c r="K293" s="5">
+        <v>43</v>
+      </c>
+      <c r="L293" s="5">
+        <v>52</v>
+      </c>
+      <c r="M293" s="5">
+        <v>28</v>
+      </c>
+      <c r="N293" s="5">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="294" spans="1:14">
+      <c r="A294" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="B294" t="s">
+        <v>265</v>
+      </c>
+      <c r="C294" s="5">
+        <v>17</v>
+      </c>
+      <c r="D294" s="5">
+        <v>6</v>
+      </c>
+      <c r="E294" s="5">
+        <v>3</v>
+      </c>
+      <c r="F294" s="5">
+        <v>50</v>
+      </c>
+      <c r="G294" s="5">
+        <v>46</v>
+      </c>
+      <c r="H294" s="5">
+        <v>45</v>
+      </c>
+      <c r="I294" s="5">
+        <v>8</v>
+      </c>
+      <c r="J294" s="5">
+        <v>26</v>
+      </c>
+      <c r="K294" s="5">
+        <v>35</v>
+      </c>
+      <c r="L294" s="5">
+        <v>41</v>
+      </c>
+      <c r="M294" s="5">
+        <v>23</v>
+      </c>
+      <c r="N294" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="295" spans="1:14">
+      <c r="A295" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="B295" t="s">
+        <v>265</v>
+      </c>
+      <c r="C295" s="5"/>
+      <c r="D295" s="5"/>
+      <c r="E295" s="5"/>
+      <c r="F295" s="5"/>
+      <c r="G295" s="5"/>
+      <c r="H295" s="5"/>
+      <c r="I295" s="5"/>
+      <c r="J295" s="5"/>
+      <c r="K295" s="5"/>
+      <c r="L295" s="5"/>
+      <c r="M295" s="5">
+        <v>2</v>
+      </c>
+      <c r="N295" s="5"/>
+    </row>
+    <row r="296" spans="1:14">
+      <c r="A296" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="B296" t="s">
+        <v>265</v>
+      </c>
+      <c r="C296" s="5"/>
+      <c r="D296" s="5"/>
+      <c r="E296" s="5"/>
+      <c r="F296" s="5"/>
+      <c r="G296" s="5"/>
+      <c r="H296" s="5"/>
+      <c r="I296" s="5"/>
+      <c r="J296" s="5"/>
+      <c r="K296" s="5"/>
+      <c r="L296" s="5"/>
+      <c r="M296" s="5">
+        <v>2</v>
+      </c>
+      <c r="N296" s="5"/>
+    </row>
+    <row r="297" spans="1:14">
+      <c r="A297" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="B297" t="s">
+        <v>265</v>
+      </c>
+      <c r="C297" s="5"/>
+      <c r="D297" s="5"/>
+      <c r="E297" s="5"/>
+      <c r="F297" s="5"/>
+      <c r="G297" s="5"/>
+      <c r="H297" s="5"/>
+      <c r="I297" s="5"/>
+      <c r="J297" s="5"/>
+      <c r="K297" s="5"/>
+      <c r="L297" s="5"/>
+      <c r="M297" s="5">
+        <v>2</v>
+      </c>
+      <c r="N297" s="5"/>
+    </row>
+    <row r="298" spans="1:14">
+      <c r="A298" s="8" t="s">
+        <v>268</v>
+      </c>
+      <c r="B298" t="s">
+        <v>265</v>
+      </c>
+      <c r="C298" s="5"/>
+      <c r="D298" s="5"/>
+      <c r="E298" s="5"/>
+      <c r="F298" s="5"/>
+      <c r="G298" s="5"/>
+      <c r="H298" s="5"/>
+      <c r="I298" s="5"/>
+      <c r="J298" s="5"/>
+      <c r="K298" s="5"/>
+      <c r="L298" s="5"/>
+      <c r="M298" s="5">
+        <v>2</v>
+      </c>
+      <c r="N298" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
